--- a/ndhu/蕭義龍/金融資料探勘_助教初評.xlsx
+++ b/ndhu/蕭義龍/金融資料探勘_助教初評.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Personal-Project\ndhu\蕭義龍\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinc./GitHub/Personal-Project/ndhu/蕭義龍/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D572FC6A-8175-4AE3-B33E-109C85AFAAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79601DBB-C67F-5349-87E9-8FD5EE20FEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" r:id="rId1"/>
@@ -24,15 +24,32 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HW1 初評'!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">低分複核!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">學生個別明細!$A$1:$G$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">期中初評!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">評分規準!$A$1:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">學生個別明細!$A$1:$G$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">檔案分數明細!$A$1:$I$360</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">總覽!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">評分規準!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={B79E9915-FACC-674A-8E6C-4D27B58E0B71}</author>
+  </authors>
+  <commentList>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{B79E9915-FACC-674A-8E6C-4D27B58E0B71}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    要加分，他的每個cell都不同</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1677,11 +1694,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1695,13 +1712,13 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1716,6 +1733,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1747,7 +1770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1759,9 +1782,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1817,6 +1843,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="陳信全" id="{D4BD8F47-CD69-B04D-9925-51F6E87185FE}" userId="S::611236017@o365.ndhu.edu.tw::2155c7cb-47ca-4739-a443-d680bf8e8dd4" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2102,18 +2134,26 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B14" dT="2026-05-14T03:19:52.43" personId="{D4BD8F47-CD69-B04D-9925-51F6E87185FE}" id="{B79E9915-FACC-674A-8E6C-4D27B58E0B71}">
+    <text>要加分，他的每個cell都不同</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2130,7 +2170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2147,7 +2187,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2164,14 +2204,14 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -2182,7 +2222,7 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="48">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -2193,7 +2233,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="63" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="48">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -2204,7 +2244,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="32">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -2215,7 +2255,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="48">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -2226,7 +2266,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="48">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -2245,9 +2285,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2260,7 +2300,7 @@
     <col min="10" max="10" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,7 +2332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="48" customHeight="1">
       <c r="A2" s="2">
         <v>411042033</v>
       </c>
@@ -2324,7 +2364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="48" customHeight="1">
       <c r="A3" s="2">
         <v>411111211</v>
       </c>
@@ -2356,12 +2396,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="48" customHeight="1">
       <c r="A4" s="2">
         <v>411111220</v>
       </c>
-      <c r="B4" s="2">
-        <v>91</v>
+      <c r="B4" s="5">
+        <v>98</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>35</v>
@@ -2388,7 +2428,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="48" customHeight="1">
       <c r="A5" s="2">
         <v>411121265</v>
       </c>
@@ -2420,7 +2460,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="48" customHeight="1">
       <c r="A6" s="2">
         <v>411121267</v>
       </c>
@@ -2452,7 +2492,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="48" customHeight="1">
       <c r="A7" s="2">
         <v>411136028</v>
       </c>
@@ -2484,7 +2524,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="48" customHeight="1">
       <c r="A8" s="2">
         <v>411236002</v>
       </c>
@@ -2516,7 +2556,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="48" customHeight="1">
       <c r="A9" s="2">
         <v>411236005</v>
       </c>
@@ -2546,7 +2586,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="48" customHeight="1">
       <c r="A10" s="2">
         <v>411236006</v>
       </c>
@@ -2576,7 +2616,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="48" customHeight="1">
       <c r="A11" s="2">
         <v>411236022</v>
       </c>
@@ -2606,7 +2646,7 @@
       </c>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="48" customHeight="1">
       <c r="A12" s="2">
         <v>411236023</v>
       </c>
@@ -2638,7 +2678,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="48" customHeight="1">
       <c r="A13" s="2">
         <v>411236057</v>
       </c>
@@ -2670,11 +2710,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="2">
         <v>411336001</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="5">
         <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2702,7 +2742,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="48" customHeight="1">
       <c r="A15" s="2">
         <v>411336004</v>
       </c>
@@ -2734,12 +2774,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="48" customHeight="1">
       <c r="A16" s="2">
         <v>411336011</v>
       </c>
-      <c r="B16" s="2">
-        <v>83</v>
+      <c r="B16" s="5">
+        <v>84</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
@@ -2766,7 +2806,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="48" customHeight="1">
       <c r="A17" s="2">
         <v>411336017</v>
       </c>
@@ -2798,7 +2838,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="2">
         <v>411336018</v>
       </c>
@@ -2830,7 +2870,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="48" customHeight="1">
       <c r="A19" s="2">
         <v>411336019</v>
       </c>
@@ -2862,7 +2902,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="48" customHeight="1">
       <c r="A20" s="2">
         <v>411336020</v>
       </c>
@@ -2894,7 +2934,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="48" customHeight="1">
       <c r="A21" s="2">
         <v>411336021</v>
       </c>
@@ -2926,7 +2966,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="48" customHeight="1">
       <c r="A22" s="2">
         <v>411336035</v>
       </c>
@@ -2958,7 +2998,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="48" customHeight="1">
       <c r="A23" s="2">
         <v>411336039</v>
       </c>
@@ -2990,7 +3030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="48" customHeight="1">
       <c r="A24" s="2">
         <v>411336043</v>
       </c>
@@ -3020,7 +3060,7 @@
       </c>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="48" customHeight="1">
       <c r="A25" s="2">
         <v>411336045</v>
       </c>
@@ -3052,7 +3092,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="48" customHeight="1">
       <c r="A26" s="2">
         <v>411336054</v>
       </c>
@@ -3084,7 +3124,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="48" customHeight="1">
       <c r="A27" s="2">
         <v>411336062</v>
       </c>
@@ -3116,7 +3156,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="48" customHeight="1">
       <c r="A28" s="2">
         <v>411336064</v>
       </c>
@@ -3149,7 +3189,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J28" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:J28" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J28">
+      <sortCondition ref="A1:A28"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B2:B28">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
@@ -3164,13 +3208,14 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -3183,7 +3228,7 @@
     <col min="10" max="10" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -3215,7 +3260,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="48" customHeight="1">
       <c r="A2" s="2">
         <v>411042033</v>
       </c>
@@ -3247,7 +3292,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="48" customHeight="1">
       <c r="A3" s="2">
         <v>411111211</v>
       </c>
@@ -3279,7 +3324,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="48" customHeight="1">
       <c r="A4" s="2">
         <v>411111220</v>
       </c>
@@ -3311,7 +3356,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="48" customHeight="1">
       <c r="A5" s="2">
         <v>411121265</v>
       </c>
@@ -3343,7 +3388,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="48" customHeight="1">
       <c r="A6" s="2">
         <v>411121267</v>
       </c>
@@ -3375,7 +3420,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="48" customHeight="1">
       <c r="A7" s="2">
         <v>411136025</v>
       </c>
@@ -3407,7 +3452,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="48" customHeight="1">
       <c r="A8" s="2">
         <v>411136028</v>
       </c>
@@ -3437,7 +3482,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="48" customHeight="1">
       <c r="A9" s="2">
         <v>411236002</v>
       </c>
@@ -3469,7 +3514,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="4" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="4" customFormat="1" ht="48" customHeight="1">
       <c r="A10" s="3">
         <v>411236005</v>
       </c>
@@ -3501,7 +3546,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="48" customHeight="1">
       <c r="A11" s="2">
         <v>411236006</v>
       </c>
@@ -3533,7 +3578,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="48" customHeight="1">
       <c r="A12" s="2">
         <v>411236022</v>
       </c>
@@ -3565,7 +3610,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="48" customHeight="1">
       <c r="A13" s="2">
         <v>411236023</v>
       </c>
@@ -3597,7 +3642,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="4" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" s="4" customFormat="1" ht="48" customHeight="1">
       <c r="A14" s="3">
         <v>411236052</v>
       </c>
@@ -3629,7 +3674,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="48" customHeight="1">
       <c r="A15" s="2">
         <v>411236057</v>
       </c>
@@ -3661,7 +3706,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="48" customHeight="1">
       <c r="A16" s="2">
         <v>411336001</v>
       </c>
@@ -3693,7 +3738,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="48" customHeight="1">
       <c r="A17" s="2">
         <v>411336004</v>
       </c>
@@ -3725,7 +3770,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="2">
         <v>411336011</v>
       </c>
@@ -3757,7 +3802,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="48" customHeight="1">
       <c r="A19" s="2">
         <v>411336017</v>
       </c>
@@ -3789,7 +3834,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="48" customHeight="1">
       <c r="A20" s="2">
         <v>411336018</v>
       </c>
@@ -3821,7 +3866,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="48" customHeight="1">
       <c r="A21" s="2">
         <v>411336020</v>
       </c>
@@ -3853,7 +3898,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="48" customHeight="1">
       <c r="A22" s="2">
         <v>411336021</v>
       </c>
@@ -3885,7 +3930,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="48" customHeight="1">
       <c r="A23" s="2">
         <v>411336035</v>
       </c>
@@ -3917,7 +3962,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="48" customHeight="1">
       <c r="A24" s="2">
         <v>411336039</v>
       </c>
@@ -3949,7 +3994,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="48" customHeight="1">
       <c r="A25" s="2">
         <v>411336043</v>
       </c>
@@ -3981,7 +4026,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="48" customHeight="1">
       <c r="A26" s="2">
         <v>411336045</v>
       </c>
@@ -4013,7 +4058,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="48" customHeight="1">
       <c r="A27" s="2">
         <v>411336054</v>
       </c>
@@ -4045,7 +4090,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="48" customHeight="1">
       <c r="A28" s="2">
         <v>411336062</v>
       </c>
@@ -4077,7 +4122,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="48" customHeight="1">
       <c r="A29" s="2">
         <v>411336064</v>
       </c>
@@ -4131,7 +4176,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I360"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -4143,7 +4188,7 @@
     <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4172,7 +4217,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -4197,7 +4242,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="48" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -4224,7 +4269,7 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="48" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -4249,7 +4294,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="48" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -4276,7 +4321,7 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="48" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -4303,7 +4348,7 @@
       </c>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="48" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -4328,7 +4373,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="48" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -4355,7 +4400,7 @@
       </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="48" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -4380,7 +4425,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="48" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -4405,7 +4450,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="48" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -4430,7 +4475,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="48" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -4455,7 +4500,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="48" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -4482,7 +4527,7 @@
       </c>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="48" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -4507,7 +4552,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="48" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -4532,7 +4577,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="48" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
@@ -4557,7 +4602,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="48" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -4582,7 +4627,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="48" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -4609,7 +4654,7 @@
       </c>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="48" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
@@ -4634,7 +4679,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="48" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
@@ -4659,7 +4704,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="48" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
@@ -4686,7 +4731,7 @@
       </c>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="48" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -4711,7 +4756,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="48" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
@@ -4738,7 +4783,7 @@
       </c>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="48" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
@@ -4763,7 +4808,7 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="48" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>5</v>
       </c>
@@ -4788,7 +4833,7 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="48" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -4813,7 +4858,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="48" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
@@ -4838,7 +4883,7 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="48" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>5</v>
       </c>
@@ -4865,7 +4910,7 @@
       </c>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="48" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
@@ -4890,7 +4935,7 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="48" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>5</v>
       </c>
@@ -4915,7 +4960,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="48" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>5</v>
       </c>
@@ -4942,7 +4987,7 @@
       </c>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="48" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
@@ -4967,7 +5012,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="48" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
@@ -4994,7 +5039,7 @@
       </c>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="48" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -5019,7 +5064,7 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="48" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>5</v>
       </c>
@@ -5044,7 +5089,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="48" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>5</v>
       </c>
@@ -5069,7 +5114,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="48" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>5</v>
       </c>
@@ -5094,7 +5139,7 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="48" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>5</v>
       </c>
@@ -5119,7 +5164,7 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="48" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>5</v>
       </c>
@@ -5144,7 +5189,7 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="48" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>5</v>
       </c>
@@ -5169,7 +5214,7 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="48" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>5</v>
       </c>
@@ -5194,7 +5239,7 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="48" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
@@ -5219,7 +5264,7 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="48" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>5</v>
       </c>
@@ -5244,7 +5289,7 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="48" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>5</v>
       </c>
@@ -5269,7 +5314,7 @@
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="48" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>5</v>
       </c>
@@ -5294,7 +5339,7 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="48" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>5</v>
       </c>
@@ -5319,7 +5364,7 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="48" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>5</v>
       </c>
@@ -5344,7 +5389,7 @@
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
     </row>
-    <row r="48" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="48" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>5</v>
       </c>
@@ -5369,7 +5414,7 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
     </row>
-    <row r="49" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="48" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>5</v>
       </c>
@@ -5394,7 +5439,7 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="48" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -5419,7 +5464,7 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="48" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>5</v>
       </c>
@@ -5444,7 +5489,7 @@
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="48" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>5</v>
       </c>
@@ -5469,7 +5514,7 @@
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
     </row>
-    <row r="53" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="48" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>5</v>
       </c>
@@ -5496,7 +5541,7 @@
       </c>
       <c r="I53" s="2"/>
     </row>
-    <row r="54" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="48" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>5</v>
       </c>
@@ -5523,7 +5568,7 @@
       </c>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="48" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>5</v>
       </c>
@@ -5550,7 +5595,7 @@
       </c>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="48" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>5</v>
       </c>
@@ -5577,7 +5622,7 @@
       </c>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="48" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>5</v>
       </c>
@@ -5602,7 +5647,7 @@
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
     </row>
-    <row r="58" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="48" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -5629,7 +5674,7 @@
       </c>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="48" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>5</v>
       </c>
@@ -5656,7 +5701,7 @@
       </c>
       <c r="I59" s="2"/>
     </row>
-    <row r="60" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="48" customHeight="1">
       <c r="A60" s="2" t="s">
         <v>5</v>
       </c>
@@ -5683,7 +5728,7 @@
       </c>
       <c r="I60" s="2"/>
     </row>
-    <row r="61" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="48" customHeight="1">
       <c r="A61" s="2" t="s">
         <v>5</v>
       </c>
@@ -5708,7 +5753,7 @@
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
     </row>
-    <row r="62" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="48" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>5</v>
       </c>
@@ -5733,7 +5778,7 @@
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
     </row>
-    <row r="63" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="48" customHeight="1">
       <c r="A63" s="2" t="s">
         <v>5</v>
       </c>
@@ -5760,7 +5805,7 @@
       </c>
       <c r="I63" s="2"/>
     </row>
-    <row r="64" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="48" customHeight="1">
       <c r="A64" s="2" t="s">
         <v>5</v>
       </c>
@@ -5785,7 +5830,7 @@
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
     </row>
-    <row r="65" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="48" customHeight="1">
       <c r="A65" s="2" t="s">
         <v>5</v>
       </c>
@@ -5810,7 +5855,7 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
     </row>
-    <row r="66" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="48" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>5</v>
       </c>
@@ -5835,7 +5880,7 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
     </row>
-    <row r="67" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="48" customHeight="1">
       <c r="A67" s="2" t="s">
         <v>5</v>
       </c>
@@ -5860,7 +5905,7 @@
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
     </row>
-    <row r="68" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="48" customHeight="1">
       <c r="A68" s="2" t="s">
         <v>5</v>
       </c>
@@ -5887,7 +5932,7 @@
       </c>
       <c r="I68" s="2"/>
     </row>
-    <row r="69" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="48" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>5</v>
       </c>
@@ -5914,7 +5959,7 @@
       </c>
       <c r="I69" s="2"/>
     </row>
-    <row r="70" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="48" customHeight="1">
       <c r="A70" s="2" t="s">
         <v>5</v>
       </c>
@@ -5939,7 +5984,7 @@
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
     </row>
-    <row r="71" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="48" customHeight="1">
       <c r="A71" s="2" t="s">
         <v>5</v>
       </c>
@@ -5964,7 +6009,7 @@
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
     </row>
-    <row r="72" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="48" customHeight="1">
       <c r="A72" s="2" t="s">
         <v>5</v>
       </c>
@@ -5989,7 +6034,7 @@
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
     </row>
-    <row r="73" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="48" customHeight="1">
       <c r="A73" s="2" t="s">
         <v>5</v>
       </c>
@@ -6016,7 +6061,7 @@
       </c>
       <c r="I73" s="2"/>
     </row>
-    <row r="74" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="48" customHeight="1">
       <c r="A74" s="2" t="s">
         <v>5</v>
       </c>
@@ -6041,7 +6086,7 @@
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
     </row>
-    <row r="75" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="48" customHeight="1">
       <c r="A75" s="2" t="s">
         <v>5</v>
       </c>
@@ -6066,7 +6111,7 @@
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
     </row>
-    <row r="76" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="48" customHeight="1">
       <c r="A76" s="2" t="s">
         <v>5</v>
       </c>
@@ -6093,7 +6138,7 @@
       </c>
       <c r="I76" s="2"/>
     </row>
-    <row r="77" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="48" customHeight="1">
       <c r="A77" s="2" t="s">
         <v>5</v>
       </c>
@@ -6118,7 +6163,7 @@
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
     </row>
-    <row r="78" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="48" customHeight="1">
       <c r="A78" s="2" t="s">
         <v>5</v>
       </c>
@@ -6145,7 +6190,7 @@
       </c>
       <c r="I78" s="2"/>
     </row>
-    <row r="79" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="48" customHeight="1">
       <c r="A79" s="2" t="s">
         <v>5</v>
       </c>
@@ -6170,7 +6215,7 @@
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
     </row>
-    <row r="80" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="48" customHeight="1">
       <c r="A80" s="2" t="s">
         <v>5</v>
       </c>
@@ -6195,7 +6240,7 @@
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
     </row>
-    <row r="81" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="48" customHeight="1">
       <c r="A81" s="2" t="s">
         <v>5</v>
       </c>
@@ -6220,7 +6265,7 @@
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
     </row>
-    <row r="82" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="48" customHeight="1">
       <c r="A82" s="2" t="s">
         <v>5</v>
       </c>
@@ -6245,7 +6290,7 @@
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
     </row>
-    <row r="83" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="48" customHeight="1">
       <c r="A83" s="2" t="s">
         <v>5</v>
       </c>
@@ -6272,7 +6317,7 @@
       </c>
       <c r="I83" s="2"/>
     </row>
-    <row r="84" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="48" customHeight="1">
       <c r="A84" s="2" t="s">
         <v>5</v>
       </c>
@@ -6297,7 +6342,7 @@
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="48" customHeight="1">
       <c r="A85" s="2" t="s">
         <v>5</v>
       </c>
@@ -6322,7 +6367,7 @@
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="48" customHeight="1">
       <c r="A86" s="2" t="s">
         <v>5</v>
       </c>
@@ -6347,7 +6392,7 @@
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
     </row>
-    <row r="87" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="48" customHeight="1">
       <c r="A87" s="2" t="s">
         <v>5</v>
       </c>
@@ -6372,7 +6417,7 @@
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
-    <row r="88" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="48" customHeight="1">
       <c r="A88" s="2" t="s">
         <v>5</v>
       </c>
@@ -6399,7 +6444,7 @@
       </c>
       <c r="I88" s="2"/>
     </row>
-    <row r="89" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="48" customHeight="1">
       <c r="A89" s="2" t="s">
         <v>5</v>
       </c>
@@ -6424,7 +6469,7 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
     </row>
-    <row r="90" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="48" customHeight="1">
       <c r="A90" s="2" t="s">
         <v>5</v>
       </c>
@@ -6449,7 +6494,7 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
     </row>
-    <row r="91" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="48" customHeight="1">
       <c r="A91" s="2" t="s">
         <v>5</v>
       </c>
@@ -6474,7 +6519,7 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
     </row>
-    <row r="92" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="48" customHeight="1">
       <c r="A92" s="2" t="s">
         <v>5</v>
       </c>
@@ -6499,7 +6544,7 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
     </row>
-    <row r="93" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="48" customHeight="1">
       <c r="A93" s="2" t="s">
         <v>5</v>
       </c>
@@ -6526,7 +6571,7 @@
       </c>
       <c r="I93" s="2"/>
     </row>
-    <row r="94" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="48" customHeight="1">
       <c r="A94" s="2" t="s">
         <v>5</v>
       </c>
@@ -6551,7 +6596,7 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
     </row>
-    <row r="95" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="48" customHeight="1">
       <c r="A95" s="2" t="s">
         <v>5</v>
       </c>
@@ -6576,7 +6621,7 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
     </row>
-    <row r="96" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="48" customHeight="1">
       <c r="A96" s="2" t="s">
         <v>5</v>
       </c>
@@ -6601,7 +6646,7 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
     </row>
-    <row r="97" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="48" customHeight="1">
       <c r="A97" s="2" t="s">
         <v>5</v>
       </c>
@@ -6626,7 +6671,7 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
     </row>
-    <row r="98" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="48" customHeight="1">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -6653,7 +6698,7 @@
       </c>
       <c r="I98" s="2"/>
     </row>
-    <row r="99" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="48" customHeight="1">
       <c r="A99" s="2" t="s">
         <v>5</v>
       </c>
@@ -6678,7 +6723,7 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
     </row>
-    <row r="100" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="48" customHeight="1">
       <c r="A100" s="2" t="s">
         <v>5</v>
       </c>
@@ -6703,7 +6748,7 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
     </row>
-    <row r="101" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="48" customHeight="1">
       <c r="A101" s="2" t="s">
         <v>5</v>
       </c>
@@ -6728,7 +6773,7 @@
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
     </row>
-    <row r="102" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="48" customHeight="1">
       <c r="A102" s="2" t="s">
         <v>5</v>
       </c>
@@ -6755,7 +6800,7 @@
       </c>
       <c r="I102" s="2"/>
     </row>
-    <row r="103" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="48" customHeight="1">
       <c r="A103" s="2" t="s">
         <v>5</v>
       </c>
@@ -6782,7 +6827,7 @@
       </c>
       <c r="I103" s="2"/>
     </row>
-    <row r="104" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="48" customHeight="1">
       <c r="A104" s="2" t="s">
         <v>5</v>
       </c>
@@ -6807,7 +6852,7 @@
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
     </row>
-    <row r="105" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="48" customHeight="1">
       <c r="A105" s="2" t="s">
         <v>5</v>
       </c>
@@ -6832,7 +6877,7 @@
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
     </row>
-    <row r="106" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="48" customHeight="1">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -6857,7 +6902,7 @@
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
     </row>
-    <row r="107" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="48" customHeight="1">
       <c r="A107" s="2" t="s">
         <v>5</v>
       </c>
@@ -6882,7 +6927,7 @@
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
     </row>
-    <row r="108" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="48" customHeight="1">
       <c r="A108" s="2" t="s">
         <v>5</v>
       </c>
@@ -6909,7 +6954,7 @@
       </c>
       <c r="I108" s="2"/>
     </row>
-    <row r="109" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="48" customHeight="1">
       <c r="A109" s="2" t="s">
         <v>5</v>
       </c>
@@ -6934,7 +6979,7 @@
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
     </row>
-    <row r="110" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="48" customHeight="1">
       <c r="A110" s="2" t="s">
         <v>5</v>
       </c>
@@ -6959,7 +7004,7 @@
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
     </row>
-    <row r="111" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="48" customHeight="1">
       <c r="A111" s="2" t="s">
         <v>5</v>
       </c>
@@ -6984,7 +7029,7 @@
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
     </row>
-    <row r="112" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="48" customHeight="1">
       <c r="A112" s="2" t="s">
         <v>5</v>
       </c>
@@ -7009,7 +7054,7 @@
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
     </row>
-    <row r="113" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="48" customHeight="1">
       <c r="A113" s="2" t="s">
         <v>5</v>
       </c>
@@ -7034,7 +7079,7 @@
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
     </row>
-    <row r="114" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" ht="48" customHeight="1">
       <c r="A114" s="2" t="s">
         <v>5</v>
       </c>
@@ -7059,7 +7104,7 @@
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
     </row>
-    <row r="115" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="48" customHeight="1">
       <c r="A115" s="2" t="s">
         <v>5</v>
       </c>
@@ -7084,7 +7129,7 @@
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
     </row>
-    <row r="116" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="48" customHeight="1">
       <c r="A116" s="2" t="s">
         <v>5</v>
       </c>
@@ -7109,7 +7154,7 @@
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
     </row>
-    <row r="117" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="48" customHeight="1">
       <c r="A117" s="2" t="s">
         <v>5</v>
       </c>
@@ -7134,7 +7179,7 @@
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
     </row>
-    <row r="118" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="48" customHeight="1">
       <c r="A118" s="2" t="s">
         <v>5</v>
       </c>
@@ -7161,7 +7206,7 @@
       </c>
       <c r="I118" s="2"/>
     </row>
-    <row r="119" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="48" customHeight="1">
       <c r="A119" s="2" t="s">
         <v>5</v>
       </c>
@@ -7186,7 +7231,7 @@
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
     </row>
-    <row r="120" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="48" customHeight="1">
       <c r="A120" s="2" t="s">
         <v>5</v>
       </c>
@@ -7211,7 +7256,7 @@
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
     </row>
-    <row r="121" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="48" customHeight="1">
       <c r="A121" s="2" t="s">
         <v>5</v>
       </c>
@@ -7236,7 +7281,7 @@
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
     </row>
-    <row r="122" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="48" customHeight="1">
       <c r="A122" s="2" t="s">
         <v>5</v>
       </c>
@@ -7261,7 +7306,7 @@
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
     </row>
-    <row r="123" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" ht="48" customHeight="1">
       <c r="A123" s="2" t="s">
         <v>5</v>
       </c>
@@ -7288,7 +7333,7 @@
       </c>
       <c r="I123" s="2"/>
     </row>
-    <row r="124" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" ht="48" customHeight="1">
       <c r="A124" s="2" t="s">
         <v>5</v>
       </c>
@@ -7313,7 +7358,7 @@
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
     </row>
-    <row r="125" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="48" customHeight="1">
       <c r="A125" s="2" t="s">
         <v>5</v>
       </c>
@@ -7338,7 +7383,7 @@
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
     </row>
-    <row r="126" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="48" customHeight="1">
       <c r="A126" s="2" t="s">
         <v>5</v>
       </c>
@@ -7363,7 +7408,7 @@
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
     </row>
-    <row r="127" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="48" customHeight="1">
       <c r="A127" s="2" t="s">
         <v>5</v>
       </c>
@@ -7388,7 +7433,7 @@
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
     </row>
-    <row r="128" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="48" customHeight="1">
       <c r="A128" s="2" t="s">
         <v>5</v>
       </c>
@@ -7415,7 +7460,7 @@
       </c>
       <c r="I128" s="2"/>
     </row>
-    <row r="129" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="48" customHeight="1">
       <c r="A129" s="2" t="s">
         <v>5</v>
       </c>
@@ -7440,7 +7485,7 @@
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
     </row>
-    <row r="130" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="48" customHeight="1">
       <c r="A130" s="2" t="s">
         <v>5</v>
       </c>
@@ -7465,7 +7510,7 @@
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
     </row>
-    <row r="131" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" ht="48" customHeight="1">
       <c r="A131" s="2" t="s">
         <v>5</v>
       </c>
@@ -7490,7 +7535,7 @@
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
     </row>
-    <row r="132" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" ht="48" customHeight="1">
       <c r="A132" s="2" t="s">
         <v>5</v>
       </c>
@@ -7515,7 +7560,7 @@
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
     </row>
-    <row r="133" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" ht="48" customHeight="1">
       <c r="A133" s="2" t="s">
         <v>5</v>
       </c>
@@ -7542,7 +7587,7 @@
       </c>
       <c r="I133" s="2"/>
     </row>
-    <row r="134" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="48" customHeight="1">
       <c r="A134" s="2" t="s">
         <v>5</v>
       </c>
@@ -7567,7 +7612,7 @@
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
     </row>
-    <row r="135" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" ht="48" customHeight="1">
       <c r="A135" s="2" t="s">
         <v>5</v>
       </c>
@@ -7592,7 +7637,7 @@
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
     </row>
-    <row r="136" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="48" customHeight="1">
       <c r="A136" s="2" t="s">
         <v>5</v>
       </c>
@@ -7617,7 +7662,7 @@
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
     </row>
-    <row r="137" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" ht="48" customHeight="1">
       <c r="A137" s="2" t="s">
         <v>6</v>
       </c>
@@ -7642,7 +7687,7 @@
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
     </row>
-    <row r="138" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="48" customHeight="1">
       <c r="A138" s="2" t="s">
         <v>6</v>
       </c>
@@ -7667,7 +7712,7 @@
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
     </row>
-    <row r="139" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="48" customHeight="1">
       <c r="A139" s="2" t="s">
         <v>6</v>
       </c>
@@ -7692,7 +7737,7 @@
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
     </row>
-    <row r="140" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="48" customHeight="1">
       <c r="A140" s="2" t="s">
         <v>6</v>
       </c>
@@ -7719,7 +7764,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" ht="48" customHeight="1">
       <c r="A141" s="2" t="s">
         <v>6</v>
       </c>
@@ -7746,7 +7791,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="48" customHeight="1">
       <c r="A142" s="2" t="s">
         <v>6</v>
       </c>
@@ -7773,7 +7818,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="48" customHeight="1">
       <c r="A143" s="2" t="s">
         <v>6</v>
       </c>
@@ -7802,7 +7847,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="48" customHeight="1">
       <c r="A144" s="2" t="s">
         <v>6</v>
       </c>
@@ -7827,7 +7872,7 @@
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
     </row>
-    <row r="145" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="48" customHeight="1">
       <c r="A145" s="2" t="s">
         <v>6</v>
       </c>
@@ -7852,7 +7897,7 @@
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
     </row>
-    <row r="146" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="48" customHeight="1">
       <c r="A146" s="2" t="s">
         <v>6</v>
       </c>
@@ -7879,7 +7924,7 @@
       </c>
       <c r="I146" s="2"/>
     </row>
-    <row r="147" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="48" customHeight="1">
       <c r="A147" s="2" t="s">
         <v>6</v>
       </c>
@@ -7904,7 +7949,7 @@
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
     </row>
-    <row r="148" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" ht="48" customHeight="1">
       <c r="A148" s="2" t="s">
         <v>6</v>
       </c>
@@ -7931,7 +7976,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="48" customHeight="1">
       <c r="A149" s="2" t="s">
         <v>6</v>
       </c>
@@ -7958,7 +8003,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="48" customHeight="1">
       <c r="A150" s="2" t="s">
         <v>6</v>
       </c>
@@ -7985,7 +8030,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="48" customHeight="1">
       <c r="A151" s="2" t="s">
         <v>6</v>
       </c>
@@ -8012,7 +8057,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="48" customHeight="1">
       <c r="A152" s="2" t="s">
         <v>6</v>
       </c>
@@ -8037,7 +8082,7 @@
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
     </row>
-    <row r="153" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="48" customHeight="1">
       <c r="A153" s="2" t="s">
         <v>6</v>
       </c>
@@ -8064,7 +8109,7 @@
       </c>
       <c r="I153" s="2"/>
     </row>
-    <row r="154" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" ht="48" customHeight="1">
       <c r="A154" s="2" t="s">
         <v>6</v>
       </c>
@@ -8089,7 +8134,7 @@
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
     </row>
-    <row r="155" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="48" customHeight="1">
       <c r="A155" s="2" t="s">
         <v>6</v>
       </c>
@@ -8114,7 +8159,7 @@
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
     </row>
-    <row r="156" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" ht="48" customHeight="1">
       <c r="A156" s="2" t="s">
         <v>6</v>
       </c>
@@ -8141,7 +8186,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="48" customHeight="1">
       <c r="A157" s="2" t="s">
         <v>6</v>
       </c>
@@ -8168,7 +8213,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="48" customHeight="1">
       <c r="A158" s="2" t="s">
         <v>6</v>
       </c>
@@ -8195,7 +8240,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" ht="48" customHeight="1">
       <c r="A159" s="2" t="s">
         <v>6</v>
       </c>
@@ -8224,7 +8269,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" ht="48" customHeight="1">
       <c r="A160" s="2" t="s">
         <v>6</v>
       </c>
@@ -8251,7 +8296,7 @@
       </c>
       <c r="I160" s="2"/>
     </row>
-    <row r="161" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" ht="48" customHeight="1">
       <c r="A161" s="2" t="s">
         <v>6</v>
       </c>
@@ -8278,7 +8323,7 @@
       </c>
       <c r="I161" s="2"/>
     </row>
-    <row r="162" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" ht="48" customHeight="1">
       <c r="A162" s="2" t="s">
         <v>6</v>
       </c>
@@ -8305,7 +8350,7 @@
       </c>
       <c r="I162" s="2"/>
     </row>
-    <row r="163" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="48" customHeight="1">
       <c r="A163" s="2" t="s">
         <v>6</v>
       </c>
@@ -8330,7 +8375,7 @@
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
     </row>
-    <row r="164" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" ht="48" customHeight="1">
       <c r="A164" s="2" t="s">
         <v>6</v>
       </c>
@@ -8357,7 +8402,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" ht="48" customHeight="1">
       <c r="A165" s="2" t="s">
         <v>6</v>
       </c>
@@ -8384,7 +8429,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="48" customHeight="1">
       <c r="A166" s="2" t="s">
         <v>6</v>
       </c>
@@ -8411,7 +8456,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="48" customHeight="1">
       <c r="A167" s="2" t="s">
         <v>6</v>
       </c>
@@ -8438,7 +8483,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" ht="48" customHeight="1">
       <c r="A168" s="2" t="s">
         <v>6</v>
       </c>
@@ -8463,7 +8508,7 @@
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
     </row>
-    <row r="169" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" ht="48" customHeight="1">
       <c r="A169" s="2" t="s">
         <v>6</v>
       </c>
@@ -8488,7 +8533,7 @@
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
     </row>
-    <row r="170" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="48" customHeight="1">
       <c r="A170" s="2" t="s">
         <v>6</v>
       </c>
@@ -8515,7 +8560,7 @@
       </c>
       <c r="I170" s="2"/>
     </row>
-    <row r="171" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="48" customHeight="1">
       <c r="A171" s="2" t="s">
         <v>6</v>
       </c>
@@ -8540,7 +8585,7 @@
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
     </row>
-    <row r="172" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="48" customHeight="1">
       <c r="A172" s="2" t="s">
         <v>6</v>
       </c>
@@ -8567,7 +8612,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="48" customHeight="1">
       <c r="A173" s="2" t="s">
         <v>6</v>
       </c>
@@ -8594,7 +8639,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="48" customHeight="1">
       <c r="A174" s="2" t="s">
         <v>6</v>
       </c>
@@ -8621,7 +8666,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="48" customHeight="1">
       <c r="A175" s="2" t="s">
         <v>6</v>
       </c>
@@ -8648,7 +8693,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="48" customHeight="1">
       <c r="A176" s="2" t="s">
         <v>6</v>
       </c>
@@ -8675,7 +8720,7 @@
       </c>
       <c r="I176" s="2"/>
     </row>
-    <row r="177" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="48" customHeight="1">
       <c r="A177" s="2" t="s">
         <v>6</v>
       </c>
@@ -8700,7 +8745,7 @@
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
     </row>
-    <row r="178" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" ht="48" customHeight="1">
       <c r="A178" s="2" t="s">
         <v>6</v>
       </c>
@@ -8725,7 +8770,7 @@
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
     </row>
-    <row r="179" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" ht="48" customHeight="1">
       <c r="A179" s="2" t="s">
         <v>6</v>
       </c>
@@ -8750,7 +8795,7 @@
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
     </row>
-    <row r="180" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" ht="48" customHeight="1">
       <c r="A180" s="2" t="s">
         <v>6</v>
       </c>
@@ -8777,7 +8822,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="48" customHeight="1">
       <c r="A181" s="2" t="s">
         <v>6</v>
       </c>
@@ -8804,7 +8849,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="48" customHeight="1">
       <c r="A182" s="2" t="s">
         <v>6</v>
       </c>
@@ -8833,7 +8878,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="48" customHeight="1">
       <c r="A183" s="2" t="s">
         <v>6</v>
       </c>
@@ -8862,7 +8907,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="48" customHeight="1">
       <c r="A184" s="2" t="s">
         <v>6</v>
       </c>
@@ -8889,7 +8934,7 @@
       </c>
       <c r="I184" s="2"/>
     </row>
-    <row r="185" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="48" customHeight="1">
       <c r="A185" s="2" t="s">
         <v>6</v>
       </c>
@@ -8914,7 +8959,7 @@
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
     </row>
-    <row r="186" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" ht="48" customHeight="1">
       <c r="A186" s="2" t="s">
         <v>6</v>
       </c>
@@ -8939,7 +8984,7 @@
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
     </row>
-    <row r="187" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="48" customHeight="1">
       <c r="A187" s="2" t="s">
         <v>6</v>
       </c>
@@ -8964,7 +9009,7 @@
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
     </row>
-    <row r="188" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="48" customHeight="1">
       <c r="A188" s="2" t="s">
         <v>6</v>
       </c>
@@ -8991,7 +9036,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="48" customHeight="1">
       <c r="A189" s="2" t="s">
         <v>6</v>
       </c>
@@ -9018,7 +9063,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" ht="48" customHeight="1">
       <c r="A190" s="2" t="s">
         <v>6</v>
       </c>
@@ -9045,7 +9090,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="48" customHeight="1">
       <c r="A191" s="2" t="s">
         <v>6</v>
       </c>
@@ -9072,7 +9117,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="48" customHeight="1">
       <c r="A192" s="2" t="s">
         <v>6</v>
       </c>
@@ -9097,7 +9142,7 @@
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
     </row>
-    <row r="193" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="48" customHeight="1">
       <c r="A193" s="2" t="s">
         <v>6</v>
       </c>
@@ -9124,7 +9169,7 @@
       </c>
       <c r="I193" s="2"/>
     </row>
-    <row r="194" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="48" customHeight="1">
       <c r="A194" s="2" t="s">
         <v>6</v>
       </c>
@@ -9151,7 +9196,7 @@
       </c>
       <c r="I194" s="2"/>
     </row>
-    <row r="195" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="48" customHeight="1">
       <c r="A195" s="2" t="s">
         <v>6</v>
       </c>
@@ -9176,7 +9221,7 @@
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
     </row>
-    <row r="196" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="48" customHeight="1">
       <c r="A196" s="2" t="s">
         <v>6</v>
       </c>
@@ -9203,7 +9248,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="48" customHeight="1">
       <c r="A197" s="2" t="s">
         <v>6</v>
       </c>
@@ -9230,7 +9275,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="48" customHeight="1">
       <c r="A198" s="2" t="s">
         <v>6</v>
       </c>
@@ -9257,7 +9302,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="48" customHeight="1">
       <c r="A199" s="2" t="s">
         <v>6</v>
       </c>
@@ -9286,7 +9331,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="48" customHeight="1">
       <c r="A200" s="2" t="s">
         <v>6</v>
       </c>
@@ -9313,7 +9358,7 @@
       </c>
       <c r="I200" s="2"/>
     </row>
-    <row r="201" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="48" customHeight="1">
       <c r="A201" s="2" t="s">
         <v>6</v>
       </c>
@@ -9340,7 +9385,7 @@
       </c>
       <c r="I201" s="2"/>
     </row>
-    <row r="202" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="48" customHeight="1">
       <c r="A202" s="2" t="s">
         <v>6</v>
       </c>
@@ -9367,7 +9412,7 @@
       </c>
       <c r="I202" s="2"/>
     </row>
-    <row r="203" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="48" customHeight="1">
       <c r="A203" s="2" t="s">
         <v>6</v>
       </c>
@@ -9394,7 +9439,7 @@
       </c>
       <c r="I203" s="2"/>
     </row>
-    <row r="204" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" ht="48" customHeight="1">
       <c r="A204" s="2" t="s">
         <v>6</v>
       </c>
@@ -9421,7 +9466,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" ht="48" customHeight="1">
       <c r="A205" s="2" t="s">
         <v>6</v>
       </c>
@@ -9448,7 +9493,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" ht="48" customHeight="1">
       <c r="A206" s="2" t="s">
         <v>6</v>
       </c>
@@ -9475,7 +9520,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" ht="48" customHeight="1">
       <c r="A207" s="2" t="s">
         <v>6</v>
       </c>
@@ -9504,7 +9549,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" ht="48" customHeight="1">
       <c r="A208" s="2" t="s">
         <v>6</v>
       </c>
@@ -9529,7 +9574,7 @@
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
     </row>
-    <row r="209" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="48" customHeight="1">
       <c r="A209" s="2" t="s">
         <v>6</v>
       </c>
@@ -9554,7 +9599,7 @@
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
     </row>
-    <row r="210" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" ht="48" customHeight="1">
       <c r="A210" s="2" t="s">
         <v>6</v>
       </c>
@@ -9579,7 +9624,7 @@
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
     </row>
-    <row r="211" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" ht="48" customHeight="1">
       <c r="A211" s="2" t="s">
         <v>6</v>
       </c>
@@ -9604,7 +9649,7 @@
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
     </row>
-    <row r="212" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" ht="48" customHeight="1">
       <c r="A212" s="2" t="s">
         <v>6</v>
       </c>
@@ -9631,7 +9676,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="48" customHeight="1">
       <c r="A213" s="2" t="s">
         <v>6</v>
       </c>
@@ -9658,7 +9703,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="48" customHeight="1">
       <c r="A214" s="2" t="s">
         <v>6</v>
       </c>
@@ -9685,7 +9730,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="48" customHeight="1">
       <c r="A215" s="2" t="s">
         <v>6</v>
       </c>
@@ -9714,7 +9759,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="48" customHeight="1">
       <c r="A216" s="2" t="s">
         <v>6</v>
       </c>
@@ -9739,7 +9784,7 @@
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
     </row>
-    <row r="217" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" ht="48" customHeight="1">
       <c r="A217" s="2" t="s">
         <v>6</v>
       </c>
@@ -9764,7 +9809,7 @@
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
     </row>
-    <row r="218" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" ht="48" customHeight="1">
       <c r="A218" s="2" t="s">
         <v>6</v>
       </c>
@@ -9791,7 +9836,7 @@
       </c>
       <c r="I218" s="2"/>
     </row>
-    <row r="219" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" ht="48" customHeight="1">
       <c r="A219" s="2" t="s">
         <v>6</v>
       </c>
@@ -9818,7 +9863,7 @@
       </c>
       <c r="I219" s="2"/>
     </row>
-    <row r="220" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="48" customHeight="1">
       <c r="A220" s="2" t="s">
         <v>6</v>
       </c>
@@ -9845,7 +9890,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="48" customHeight="1">
       <c r="A221" s="2" t="s">
         <v>6</v>
       </c>
@@ -9872,7 +9917,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="48" customHeight="1">
       <c r="A222" s="2" t="s">
         <v>6</v>
       </c>
@@ -9899,7 +9944,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" ht="48" customHeight="1">
       <c r="A223" s="2" t="s">
         <v>6</v>
       </c>
@@ -9928,7 +9973,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" ht="48" customHeight="1">
       <c r="A224" s="2" t="s">
         <v>6</v>
       </c>
@@ -9953,7 +9998,7 @@
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
     </row>
-    <row r="225" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="48" customHeight="1">
       <c r="A225" s="2" t="s">
         <v>6</v>
       </c>
@@ -9980,7 +10025,7 @@
       </c>
       <c r="I225" s="2"/>
     </row>
-    <row r="226" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="48" customHeight="1">
       <c r="A226" s="2" t="s">
         <v>6</v>
       </c>
@@ -10007,7 +10052,7 @@
       </c>
       <c r="I226" s="2"/>
     </row>
-    <row r="227" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="48" customHeight="1">
       <c r="A227" s="2" t="s">
         <v>6</v>
       </c>
@@ -10034,7 +10079,7 @@
       </c>
       <c r="I227" s="2"/>
     </row>
-    <row r="228" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" ht="48" customHeight="1">
       <c r="A228" s="2" t="s">
         <v>6</v>
       </c>
@@ -10061,7 +10106,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" ht="48" customHeight="1">
       <c r="A229" s="2" t="s">
         <v>6</v>
       </c>
@@ -10088,7 +10133,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" ht="48" customHeight="1">
       <c r="A230" s="2" t="s">
         <v>6</v>
       </c>
@@ -10115,7 +10160,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="48" customHeight="1">
       <c r="A231" s="2" t="s">
         <v>6</v>
       </c>
@@ -10144,7 +10189,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="48" customHeight="1">
       <c r="A232" s="2" t="s">
         <v>6</v>
       </c>
@@ -10171,7 +10216,7 @@
       </c>
       <c r="I232" s="2"/>
     </row>
-    <row r="233" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="48" customHeight="1">
       <c r="A233" s="2" t="s">
         <v>6</v>
       </c>
@@ -10198,7 +10243,7 @@
       </c>
       <c r="I233" s="2"/>
     </row>
-    <row r="234" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="48" customHeight="1">
       <c r="A234" s="2" t="s">
         <v>6</v>
       </c>
@@ -10225,7 +10270,7 @@
       </c>
       <c r="I234" s="2"/>
     </row>
-    <row r="235" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="48" customHeight="1">
       <c r="A235" s="2" t="s">
         <v>6</v>
       </c>
@@ -10250,7 +10295,7 @@
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
-    <row r="236" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" ht="48" customHeight="1">
       <c r="A236" s="2" t="s">
         <v>6</v>
       </c>
@@ -10277,7 +10322,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="48" customHeight="1">
       <c r="A237" s="2" t="s">
         <v>6</v>
       </c>
@@ -10304,7 +10349,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="48" customHeight="1">
       <c r="A238" s="2" t="s">
         <v>6</v>
       </c>
@@ -10331,7 +10376,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="48" customHeight="1">
       <c r="A239" s="2" t="s">
         <v>6</v>
       </c>
@@ -10358,7 +10403,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" ht="48" customHeight="1">
       <c r="A240" s="2" t="s">
         <v>6</v>
       </c>
@@ -10383,7 +10428,7 @@
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
     </row>
-    <row r="241" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" ht="48" customHeight="1">
       <c r="A241" s="2" t="s">
         <v>6</v>
       </c>
@@ -10410,7 +10455,7 @@
       </c>
       <c r="I241" s="2"/>
     </row>
-    <row r="242" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" ht="48" customHeight="1">
       <c r="A242" s="2" t="s">
         <v>6</v>
       </c>
@@ -10437,7 +10482,7 @@
       </c>
       <c r="I242" s="2"/>
     </row>
-    <row r="243" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" ht="48" customHeight="1">
       <c r="A243" s="2" t="s">
         <v>6</v>
       </c>
@@ -10462,7 +10507,7 @@
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
     </row>
-    <row r="244" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="48" customHeight="1">
       <c r="A244" s="2" t="s">
         <v>6</v>
       </c>
@@ -10489,7 +10534,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="48" customHeight="1">
       <c r="A245" s="2" t="s">
         <v>6</v>
       </c>
@@ -10516,7 +10561,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" ht="48" customHeight="1">
       <c r="A246" s="2" t="s">
         <v>6</v>
       </c>
@@ -10543,7 +10588,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="48" customHeight="1">
       <c r="A247" s="2" t="s">
         <v>6</v>
       </c>
@@ -10570,7 +10615,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="48" customHeight="1">
       <c r="A248" s="2" t="s">
         <v>6</v>
       </c>
@@ -10595,7 +10640,7 @@
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
     </row>
-    <row r="249" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="48" customHeight="1">
       <c r="A249" s="2" t="s">
         <v>6</v>
       </c>
@@ -10620,7 +10665,7 @@
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
     </row>
-    <row r="250" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" ht="48" customHeight="1">
       <c r="A250" s="2" t="s">
         <v>6</v>
       </c>
@@ -10647,7 +10692,7 @@
       </c>
       <c r="I250" s="2"/>
     </row>
-    <row r="251" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" ht="48" customHeight="1">
       <c r="A251" s="2" t="s">
         <v>6</v>
       </c>
@@ -10672,7 +10717,7 @@
       <c r="H251" s="2"/>
       <c r="I251" s="2"/>
     </row>
-    <row r="252" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" ht="48" customHeight="1">
       <c r="A252" s="2" t="s">
         <v>6</v>
       </c>
@@ -10699,7 +10744,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" ht="48" customHeight="1">
       <c r="A253" s="2" t="s">
         <v>6</v>
       </c>
@@ -10726,7 +10771,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" ht="48" customHeight="1">
       <c r="A254" s="2" t="s">
         <v>6</v>
       </c>
@@ -10753,7 +10798,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" ht="48" customHeight="1">
       <c r="A255" s="2" t="s">
         <v>6</v>
       </c>
@@ -10780,7 +10825,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" ht="48" customHeight="1">
       <c r="A256" s="2" t="s">
         <v>6</v>
       </c>
@@ -10805,7 +10850,7 @@
       <c r="H256" s="2"/>
       <c r="I256" s="2"/>
     </row>
-    <row r="257" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" ht="48" customHeight="1">
       <c r="A257" s="2" t="s">
         <v>6</v>
       </c>
@@ -10830,7 +10875,7 @@
       <c r="H257" s="2"/>
       <c r="I257" s="2"/>
     </row>
-    <row r="258" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" ht="48" customHeight="1">
       <c r="A258" s="2" t="s">
         <v>6</v>
       </c>
@@ -10857,7 +10902,7 @@
       </c>
       <c r="I258" s="2"/>
     </row>
-    <row r="259" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" ht="48" customHeight="1">
       <c r="A259" s="2" t="s">
         <v>6</v>
       </c>
@@ -10882,7 +10927,7 @@
       <c r="H259" s="2"/>
       <c r="I259" s="2"/>
     </row>
-    <row r="260" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" ht="48" customHeight="1">
       <c r="A260" s="2" t="s">
         <v>6</v>
       </c>
@@ -10909,7 +10954,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" ht="48" customHeight="1">
       <c r="A261" s="2" t="s">
         <v>6</v>
       </c>
@@ -10936,7 +10981,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" ht="48" customHeight="1">
       <c r="A262" s="2" t="s">
         <v>6</v>
       </c>
@@ -10963,7 +11008,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" ht="48" customHeight="1">
       <c r="A263" s="2" t="s">
         <v>6</v>
       </c>
@@ -10990,7 +11035,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" ht="48" customHeight="1">
       <c r="A264" s="2" t="s">
         <v>6</v>
       </c>
@@ -11015,7 +11060,7 @@
       <c r="H264" s="2"/>
       <c r="I264" s="2"/>
     </row>
-    <row r="265" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" ht="48" customHeight="1">
       <c r="A265" s="2" t="s">
         <v>6</v>
       </c>
@@ -11040,7 +11085,7 @@
       <c r="H265" s="2"/>
       <c r="I265" s="2"/>
     </row>
-    <row r="266" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" ht="48" customHeight="1">
       <c r="A266" s="2" t="s">
         <v>6</v>
       </c>
@@ -11067,7 +11112,7 @@
       </c>
       <c r="I266" s="2"/>
     </row>
-    <row r="267" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" ht="48" customHeight="1">
       <c r="A267" s="2" t="s">
         <v>6</v>
       </c>
@@ -11092,7 +11137,7 @@
       <c r="H267" s="2"/>
       <c r="I267" s="2"/>
     </row>
-    <row r="268" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" ht="48" customHeight="1">
       <c r="A268" s="2" t="s">
         <v>6</v>
       </c>
@@ -11119,7 +11164,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" ht="48" customHeight="1">
       <c r="A269" s="2" t="s">
         <v>6</v>
       </c>
@@ -11146,7 +11191,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" ht="48" customHeight="1">
       <c r="A270" s="2" t="s">
         <v>6</v>
       </c>
@@ -11173,7 +11218,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" ht="48" customHeight="1">
       <c r="A271" s="2" t="s">
         <v>6</v>
       </c>
@@ -11200,7 +11245,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" ht="48" customHeight="1">
       <c r="A272" s="2" t="s">
         <v>6</v>
       </c>
@@ -11225,7 +11270,7 @@
       <c r="H272" s="2"/>
       <c r="I272" s="2"/>
     </row>
-    <row r="273" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" ht="48" customHeight="1">
       <c r="A273" s="2" t="s">
         <v>6</v>
       </c>
@@ -11250,7 +11295,7 @@
       <c r="H273" s="2"/>
       <c r="I273" s="2"/>
     </row>
-    <row r="274" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" ht="48" customHeight="1">
       <c r="A274" s="2" t="s">
         <v>6</v>
       </c>
@@ -11277,7 +11322,7 @@
       </c>
       <c r="I274" s="2"/>
     </row>
-    <row r="275" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" ht="48" customHeight="1">
       <c r="A275" s="2" t="s">
         <v>6</v>
       </c>
@@ -11302,7 +11347,7 @@
       <c r="H275" s="2"/>
       <c r="I275" s="2"/>
     </row>
-    <row r="276" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" ht="48" customHeight="1">
       <c r="A276" s="2" t="s">
         <v>6</v>
       </c>
@@ -11329,7 +11374,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" ht="48" customHeight="1">
       <c r="A277" s="2" t="s">
         <v>6</v>
       </c>
@@ -11356,7 +11401,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" ht="48" customHeight="1">
       <c r="A278" s="2" t="s">
         <v>6</v>
       </c>
@@ -11383,7 +11428,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" ht="48" customHeight="1">
       <c r="A279" s="2" t="s">
         <v>6</v>
       </c>
@@ -11410,7 +11455,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" ht="48" customHeight="1">
       <c r="A280" s="2" t="s">
         <v>6</v>
       </c>
@@ -11435,7 +11480,7 @@
       <c r="H280" s="2"/>
       <c r="I280" s="2"/>
     </row>
-    <row r="281" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" ht="48" customHeight="1">
       <c r="A281" s="2" t="s">
         <v>6</v>
       </c>
@@ -11460,7 +11505,7 @@
       <c r="H281" s="2"/>
       <c r="I281" s="2"/>
     </row>
-    <row r="282" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" ht="48" customHeight="1">
       <c r="A282" s="2" t="s">
         <v>6</v>
       </c>
@@ -11487,7 +11532,7 @@
       </c>
       <c r="I282" s="2"/>
     </row>
-    <row r="283" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" ht="48" customHeight="1">
       <c r="A283" s="2" t="s">
         <v>6</v>
       </c>
@@ -11512,7 +11557,7 @@
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
     </row>
-    <row r="284" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" ht="48" customHeight="1">
       <c r="A284" s="2" t="s">
         <v>6</v>
       </c>
@@ -11539,7 +11584,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="48" customHeight="1">
       <c r="A285" s="2" t="s">
         <v>6</v>
       </c>
@@ -11566,7 +11611,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="48" customHeight="1">
       <c r="A286" s="2" t="s">
         <v>6</v>
       </c>
@@ -11593,7 +11638,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" ht="48" customHeight="1">
       <c r="A287" s="2" t="s">
         <v>6</v>
       </c>
@@ -11620,7 +11665,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" ht="48" customHeight="1">
       <c r="A288" s="2" t="s">
         <v>6</v>
       </c>
@@ -11645,7 +11690,7 @@
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
     </row>
-    <row r="289" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" ht="48" customHeight="1">
       <c r="A289" s="2" t="s">
         <v>6</v>
       </c>
@@ -11672,7 +11717,7 @@
       </c>
       <c r="I289" s="2"/>
     </row>
-    <row r="290" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" ht="48" customHeight="1">
       <c r="A290" s="2" t="s">
         <v>6</v>
       </c>
@@ -11699,7 +11744,7 @@
       </c>
       <c r="I290" s="2"/>
     </row>
-    <row r="291" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" ht="48" customHeight="1">
       <c r="A291" s="2" t="s">
         <v>6</v>
       </c>
@@ -11726,7 +11771,7 @@
       </c>
       <c r="I291" s="2"/>
     </row>
-    <row r="292" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" ht="48" customHeight="1">
       <c r="A292" s="2" t="s">
         <v>6</v>
       </c>
@@ -11753,7 +11798,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" ht="48" customHeight="1">
       <c r="A293" s="2" t="s">
         <v>6</v>
       </c>
@@ -11780,7 +11825,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" ht="48" customHeight="1">
       <c r="A294" s="2" t="s">
         <v>6</v>
       </c>
@@ -11807,7 +11852,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" ht="48" customHeight="1">
       <c r="A295" s="2" t="s">
         <v>6</v>
       </c>
@@ -11834,7 +11879,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" ht="48" customHeight="1">
       <c r="A296" s="2" t="s">
         <v>6</v>
       </c>
@@ -11859,7 +11904,7 @@
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
     </row>
-    <row r="297" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" ht="48" customHeight="1">
       <c r="A297" s="2" t="s">
         <v>6</v>
       </c>
@@ -11884,7 +11929,7 @@
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
     </row>
-    <row r="298" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" ht="48" customHeight="1">
       <c r="A298" s="2" t="s">
         <v>6</v>
       </c>
@@ -11911,7 +11956,7 @@
       </c>
       <c r="I298" s="2"/>
     </row>
-    <row r="299" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" ht="48" customHeight="1">
       <c r="A299" s="2" t="s">
         <v>6</v>
       </c>
@@ -11936,7 +11981,7 @@
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
     </row>
-    <row r="300" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" ht="48" customHeight="1">
       <c r="A300" s="2" t="s">
         <v>6</v>
       </c>
@@ -11963,7 +12008,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" ht="48" customHeight="1">
       <c r="A301" s="2" t="s">
         <v>6</v>
       </c>
@@ -11990,7 +12035,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" ht="48" customHeight="1">
       <c r="A302" s="2" t="s">
         <v>6</v>
       </c>
@@ -12017,7 +12062,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" ht="48" customHeight="1">
       <c r="A303" s="2" t="s">
         <v>6</v>
       </c>
@@ -12044,7 +12089,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" ht="48" customHeight="1">
       <c r="A304" s="2" t="s">
         <v>6</v>
       </c>
@@ -12069,7 +12114,7 @@
       <c r="H304" s="2"/>
       <c r="I304" s="2"/>
     </row>
-    <row r="305" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" ht="48" customHeight="1">
       <c r="A305" s="2" t="s">
         <v>6</v>
       </c>
@@ -12094,7 +12139,7 @@
       <c r="H305" s="2"/>
       <c r="I305" s="2"/>
     </row>
-    <row r="306" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" ht="48" customHeight="1">
       <c r="A306" s="2" t="s">
         <v>6</v>
       </c>
@@ -12121,7 +12166,7 @@
       </c>
       <c r="I306" s="2"/>
     </row>
-    <row r="307" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" ht="48" customHeight="1">
       <c r="A307" s="2" t="s">
         <v>6</v>
       </c>
@@ -12146,7 +12191,7 @@
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
     </row>
-    <row r="308" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" ht="48" customHeight="1">
       <c r="A308" s="2" t="s">
         <v>6</v>
       </c>
@@ -12173,7 +12218,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" ht="48" customHeight="1">
       <c r="A309" s="2" t="s">
         <v>6</v>
       </c>
@@ -12200,7 +12245,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" ht="48" customHeight="1">
       <c r="A310" s="2" t="s">
         <v>6</v>
       </c>
@@ -12227,7 +12272,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" ht="48" customHeight="1">
       <c r="A311" s="2" t="s">
         <v>6</v>
       </c>
@@ -12254,7 +12299,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" ht="48" customHeight="1">
       <c r="A312" s="2" t="s">
         <v>6</v>
       </c>
@@ -12281,7 +12326,7 @@
       </c>
       <c r="I312" s="2"/>
     </row>
-    <row r="313" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" ht="48" customHeight="1">
       <c r="A313" s="2" t="s">
         <v>6</v>
       </c>
@@ -12306,7 +12351,7 @@
       <c r="H313" s="2"/>
       <c r="I313" s="2"/>
     </row>
-    <row r="314" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" ht="48" customHeight="1">
       <c r="A314" s="2" t="s">
         <v>6</v>
       </c>
@@ -12333,7 +12378,7 @@
       </c>
       <c r="I314" s="2"/>
     </row>
-    <row r="315" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" ht="48" customHeight="1">
       <c r="A315" s="2" t="s">
         <v>6</v>
       </c>
@@ -12358,7 +12403,7 @@
       <c r="H315" s="2"/>
       <c r="I315" s="2"/>
     </row>
-    <row r="316" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" ht="48" customHeight="1">
       <c r="A316" s="2" t="s">
         <v>6</v>
       </c>
@@ -12385,7 +12430,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" ht="48" customHeight="1">
       <c r="A317" s="2" t="s">
         <v>6</v>
       </c>
@@ -12412,7 +12457,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" ht="48" customHeight="1">
       <c r="A318" s="2" t="s">
         <v>6</v>
       </c>
@@ -12439,7 +12484,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" ht="48" customHeight="1">
       <c r="A319" s="2" t="s">
         <v>6</v>
       </c>
@@ -12466,7 +12511,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" ht="48" customHeight="1">
       <c r="A320" s="2" t="s">
         <v>6</v>
       </c>
@@ -12491,7 +12536,7 @@
       <c r="H320" s="2"/>
       <c r="I320" s="2"/>
     </row>
-    <row r="321" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" ht="48" customHeight="1">
       <c r="A321" s="2" t="s">
         <v>6</v>
       </c>
@@ -12518,7 +12563,7 @@
       </c>
       <c r="I321" s="2"/>
     </row>
-    <row r="322" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" ht="48" customHeight="1">
       <c r="A322" s="2" t="s">
         <v>6</v>
       </c>
@@ -12545,7 +12590,7 @@
       </c>
       <c r="I322" s="2"/>
     </row>
-    <row r="323" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" ht="48" customHeight="1">
       <c r="A323" s="2" t="s">
         <v>6</v>
       </c>
@@ -12570,7 +12615,7 @@
       <c r="H323" s="2"/>
       <c r="I323" s="2"/>
     </row>
-    <row r="324" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" ht="48" customHeight="1">
       <c r="A324" s="2" t="s">
         <v>6</v>
       </c>
@@ -12597,7 +12642,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" ht="48" customHeight="1">
       <c r="A325" s="2" t="s">
         <v>6</v>
       </c>
@@ -12624,7 +12669,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" ht="48" customHeight="1">
       <c r="A326" s="2" t="s">
         <v>6</v>
       </c>
@@ -12651,7 +12696,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" ht="48" customHeight="1">
       <c r="A327" s="2" t="s">
         <v>6</v>
       </c>
@@ -12680,7 +12725,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" ht="48" customHeight="1">
       <c r="A328" s="2" t="s">
         <v>6</v>
       </c>
@@ -12705,7 +12750,7 @@
       <c r="H328" s="2"/>
       <c r="I328" s="2"/>
     </row>
-    <row r="329" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" ht="48" customHeight="1">
       <c r="A329" s="2" t="s">
         <v>6</v>
       </c>
@@ -12732,7 +12777,7 @@
       </c>
       <c r="I329" s="2"/>
     </row>
-    <row r="330" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" ht="48" customHeight="1">
       <c r="A330" s="2" t="s">
         <v>6</v>
       </c>
@@ -12759,7 +12804,7 @@
       </c>
       <c r="I330" s="2"/>
     </row>
-    <row r="331" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" ht="48" customHeight="1">
       <c r="A331" s="2" t="s">
         <v>6</v>
       </c>
@@ -12784,7 +12829,7 @@
       <c r="H331" s="2"/>
       <c r="I331" s="2"/>
     </row>
-    <row r="332" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" ht="48" customHeight="1">
       <c r="A332" s="2" t="s">
         <v>6</v>
       </c>
@@ -12811,7 +12856,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" ht="48" customHeight="1">
       <c r="A333" s="2" t="s">
         <v>6</v>
       </c>
@@ -12838,7 +12883,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" ht="48" customHeight="1">
       <c r="A334" s="2" t="s">
         <v>6</v>
       </c>
@@ -12865,7 +12910,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" ht="48" customHeight="1">
       <c r="A335" s="2" t="s">
         <v>6</v>
       </c>
@@ -12894,7 +12939,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" ht="48" customHeight="1">
       <c r="A336" s="2" t="s">
         <v>6</v>
       </c>
@@ -12919,7 +12964,7 @@
       <c r="H336" s="2"/>
       <c r="I336" s="2"/>
     </row>
-    <row r="337" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" ht="48" customHeight="1">
       <c r="A337" s="2" t="s">
         <v>6</v>
       </c>
@@ -12944,7 +12989,7 @@
       <c r="H337" s="2"/>
       <c r="I337" s="2"/>
     </row>
-    <row r="338" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" ht="48" customHeight="1">
       <c r="A338" s="2" t="s">
         <v>6</v>
       </c>
@@ -12971,7 +13016,7 @@
       </c>
       <c r="I338" s="2"/>
     </row>
-    <row r="339" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" ht="48" customHeight="1">
       <c r="A339" s="2" t="s">
         <v>6</v>
       </c>
@@ -12996,7 +13041,7 @@
       <c r="H339" s="2"/>
       <c r="I339" s="2"/>
     </row>
-    <row r="340" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" ht="48" customHeight="1">
       <c r="A340" s="2" t="s">
         <v>6</v>
       </c>
@@ -13023,7 +13068,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" ht="48" customHeight="1">
       <c r="A341" s="2" t="s">
         <v>6</v>
       </c>
@@ -13050,7 +13095,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" ht="48" customHeight="1">
       <c r="A342" s="2" t="s">
         <v>6</v>
       </c>
@@ -13077,7 +13122,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" ht="48" customHeight="1">
       <c r="A343" s="2" t="s">
         <v>6</v>
       </c>
@@ -13104,7 +13149,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" ht="48" customHeight="1">
       <c r="A344" s="2" t="s">
         <v>6</v>
       </c>
@@ -13129,7 +13174,7 @@
       <c r="H344" s="2"/>
       <c r="I344" s="2"/>
     </row>
-    <row r="345" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" ht="48" customHeight="1">
       <c r="A345" s="2" t="s">
         <v>6</v>
       </c>
@@ -13154,7 +13199,7 @@
       <c r="H345" s="2"/>
       <c r="I345" s="2"/>
     </row>
-    <row r="346" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" ht="48" customHeight="1">
       <c r="A346" s="2" t="s">
         <v>6</v>
       </c>
@@ -13181,7 +13226,7 @@
       </c>
       <c r="I346" s="2"/>
     </row>
-    <row r="347" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" ht="48" customHeight="1">
       <c r="A347" s="2" t="s">
         <v>6</v>
       </c>
@@ -13206,7 +13251,7 @@
       <c r="H347" s="2"/>
       <c r="I347" s="2"/>
     </row>
-    <row r="348" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" ht="48" customHeight="1">
       <c r="A348" s="2" t="s">
         <v>6</v>
       </c>
@@ -13233,7 +13278,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" ht="48" customHeight="1">
       <c r="A349" s="2" t="s">
         <v>6</v>
       </c>
@@ -13260,7 +13305,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" ht="48" customHeight="1">
       <c r="A350" s="2" t="s">
         <v>6</v>
       </c>
@@ -13287,7 +13332,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" ht="48" customHeight="1">
       <c r="A351" s="2" t="s">
         <v>6</v>
       </c>
@@ -13314,7 +13359,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" ht="48" customHeight="1">
       <c r="A352" s="2" t="s">
         <v>6</v>
       </c>
@@ -13341,7 +13386,7 @@
       </c>
       <c r="I352" s="2"/>
     </row>
-    <row r="353" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" ht="48" customHeight="1">
       <c r="A353" s="2" t="s">
         <v>6</v>
       </c>
@@ -13366,7 +13411,7 @@
       <c r="H353" s="2"/>
       <c r="I353" s="2"/>
     </row>
-    <row r="354" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" ht="48" customHeight="1">
       <c r="A354" s="2" t="s">
         <v>6</v>
       </c>
@@ -13393,7 +13438,7 @@
       </c>
       <c r="I354" s="2"/>
     </row>
-    <row r="355" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" ht="48" customHeight="1">
       <c r="A355" s="2" t="s">
         <v>6</v>
       </c>
@@ -13418,7 +13463,7 @@
       <c r="H355" s="2"/>
       <c r="I355" s="2"/>
     </row>
-    <row r="356" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" ht="48" customHeight="1">
       <c r="A356" s="2" t="s">
         <v>6</v>
       </c>
@@ -13445,7 +13490,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" ht="48" customHeight="1">
       <c r="A357" s="2" t="s">
         <v>6</v>
       </c>
@@ -13472,7 +13517,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" ht="48" customHeight="1">
       <c r="A358" s="2" t="s">
         <v>6</v>
       </c>
@@ -13499,7 +13544,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" ht="48" customHeight="1">
       <c r="A359" s="2" t="s">
         <v>6</v>
       </c>
@@ -13526,7 +13571,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" ht="48" customHeight="1">
       <c r="A360" s="2" t="s">
         <v>6</v>
       </c>
@@ -13561,7 +13606,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="5" width="10" customWidth="1"/>
@@ -13569,7 +13614,7 @@
     <col min="7" max="7" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -13592,7 +13637,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="74" customHeight="1">
       <c r="A2" s="2">
         <v>411042033</v>
       </c>
@@ -13615,7 +13660,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="74" customHeight="1">
       <c r="A3" s="2">
         <v>411042033</v>
       </c>
@@ -13638,7 +13683,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="74" customHeight="1">
       <c r="A4" s="2">
         <v>411111211</v>
       </c>
@@ -13661,7 +13706,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="74" customHeight="1">
       <c r="A5" s="2">
         <v>411111211</v>
       </c>
@@ -13684,7 +13729,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="74" customHeight="1">
       <c r="A6" s="2">
         <v>411111220</v>
       </c>
@@ -13707,7 +13752,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="74" customHeight="1">
       <c r="A7" s="2">
         <v>411111220</v>
       </c>
@@ -13730,7 +13775,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="74" customHeight="1">
       <c r="A8" s="2">
         <v>411121265</v>
       </c>
@@ -13753,7 +13798,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="74" customHeight="1">
       <c r="A9" s="2">
         <v>411121265</v>
       </c>
@@ -13776,7 +13821,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="74" customHeight="1">
       <c r="A10" s="2">
         <v>411121267</v>
       </c>
@@ -13799,7 +13844,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="74" customHeight="1">
       <c r="A11" s="2">
         <v>411121267</v>
       </c>
@@ -13822,7 +13867,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="74" customHeight="1">
       <c r="A12" s="2">
         <v>411136025</v>
       </c>
@@ -13845,7 +13890,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="74" customHeight="1">
       <c r="A13" s="2">
         <v>411136028</v>
       </c>
@@ -13868,7 +13913,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="74" customHeight="1">
       <c r="A14" s="2">
         <v>411136028</v>
       </c>
@@ -13889,7 +13934,7 @@
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="74" customHeight="1">
       <c r="A15" s="2">
         <v>411236002</v>
       </c>
@@ -13912,7 +13957,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="74" customHeight="1">
       <c r="A16" s="2">
         <v>411236002</v>
       </c>
@@ -13935,7 +13980,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="74" customHeight="1">
       <c r="A17" s="2">
         <v>411236005</v>
       </c>
@@ -13956,7 +14001,7 @@
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="74" customHeight="1">
       <c r="A18" s="2">
         <v>411236005</v>
       </c>
@@ -13979,7 +14024,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="74" customHeight="1">
       <c r="A19" s="2">
         <v>411236006</v>
       </c>
@@ -14000,7 +14045,7 @@
       </c>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="74" customHeight="1">
       <c r="A20" s="2">
         <v>411236006</v>
       </c>
@@ -14023,7 +14068,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="74" customHeight="1">
       <c r="A21" s="2">
         <v>411236022</v>
       </c>
@@ -14044,7 +14089,7 @@
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="74" customHeight="1">
       <c r="A22" s="2">
         <v>411236022</v>
       </c>
@@ -14067,7 +14112,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="74" customHeight="1">
       <c r="A23" s="2">
         <v>411236023</v>
       </c>
@@ -14090,7 +14135,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="74" customHeight="1">
       <c r="A24" s="2">
         <v>411236023</v>
       </c>
@@ -14113,7 +14158,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="74" customHeight="1">
       <c r="A25" s="2">
         <v>411236052</v>
       </c>
@@ -14136,7 +14181,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="74" customHeight="1">
       <c r="A26" s="2">
         <v>411236057</v>
       </c>
@@ -14159,7 +14204,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="74" customHeight="1">
       <c r="A27" s="2">
         <v>411236057</v>
       </c>
@@ -14182,7 +14227,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="74" customHeight="1">
       <c r="A28" s="2">
         <v>411336001</v>
       </c>
@@ -14205,7 +14250,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="74" customHeight="1">
       <c r="A29" s="2">
         <v>411336001</v>
       </c>
@@ -14228,7 +14273,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="74" customHeight="1">
       <c r="A30" s="2">
         <v>411336004</v>
       </c>
@@ -14251,7 +14296,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="74" customHeight="1">
       <c r="A31" s="2">
         <v>411336004</v>
       </c>
@@ -14274,7 +14319,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="74" customHeight="1">
       <c r="A32" s="2">
         <v>411336011</v>
       </c>
@@ -14297,7 +14342,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="74" customHeight="1">
       <c r="A33" s="2">
         <v>411336011</v>
       </c>
@@ -14320,7 +14365,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="74" customHeight="1">
       <c r="A34" s="2">
         <v>411336017</v>
       </c>
@@ -14343,7 +14388,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="74" customHeight="1">
       <c r="A35" s="2">
         <v>411336017</v>
       </c>
@@ -14366,7 +14411,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="74" customHeight="1">
       <c r="A36" s="2">
         <v>411336018</v>
       </c>
@@ -14389,7 +14434,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="74" customHeight="1">
       <c r="A37" s="2">
         <v>411336018</v>
       </c>
@@ -14412,7 +14457,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="74" customHeight="1">
       <c r="A38" s="2">
         <v>411336019</v>
       </c>
@@ -14435,7 +14480,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="74" customHeight="1">
       <c r="A39" s="2">
         <v>411336020</v>
       </c>
@@ -14458,7 +14503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="74" customHeight="1">
       <c r="A40" s="2">
         <v>411336020</v>
       </c>
@@ -14481,7 +14526,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="74" customHeight="1">
       <c r="A41" s="2">
         <v>411336021</v>
       </c>
@@ -14504,7 +14549,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="74" customHeight="1">
       <c r="A42" s="2">
         <v>411336021</v>
       </c>
@@ -14527,7 +14572,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="74" customHeight="1">
       <c r="A43" s="2">
         <v>411336035</v>
       </c>
@@ -14550,7 +14595,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="74" customHeight="1">
       <c r="A44" s="2">
         <v>411336035</v>
       </c>
@@ -14573,7 +14618,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="74" customHeight="1">
       <c r="A45" s="2">
         <v>411336039</v>
       </c>
@@ -14596,7 +14641,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="74" customHeight="1">
       <c r="A46" s="2">
         <v>411336039</v>
       </c>
@@ -14619,7 +14664,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="74" customHeight="1">
       <c r="A47" s="2">
         <v>411336043</v>
       </c>
@@ -14640,7 +14685,7 @@
       </c>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="74" customHeight="1">
       <c r="A48" s="2">
         <v>411336043</v>
       </c>
@@ -14663,7 +14708,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="74" customHeight="1">
       <c r="A49" s="2">
         <v>411336045</v>
       </c>
@@ -14686,7 +14731,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="74" customHeight="1">
       <c r="A50" s="2">
         <v>411336045</v>
       </c>
@@ -14709,7 +14754,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="74" customHeight="1">
       <c r="A51" s="2">
         <v>411336054</v>
       </c>
@@ -14732,7 +14777,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="74" customHeight="1">
       <c r="A52" s="2">
         <v>411336054</v>
       </c>
@@ -14755,7 +14800,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="74" customHeight="1">
       <c r="A53" s="2">
         <v>411336062</v>
       </c>
@@ -14778,7 +14823,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="74" customHeight="1">
       <c r="A54" s="2">
         <v>411336062</v>
       </c>
@@ -14801,7 +14846,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="74" customHeight="1">
       <c r="A55" s="2">
         <v>411336064</v>
       </c>
@@ -14824,7 +14869,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="74" customHeight="1">
       <c r="A56" s="2">
         <v>411336064</v>
       </c>
@@ -14857,7 +14902,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -14867,7 +14912,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14887,7 +14932,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="60" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -14907,7 +14952,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="60" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -14937,7 +14982,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -14947,7 +14992,7 @@
     <col min="6" max="6" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14967,7 +15012,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="76" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -14987,7 +15032,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="76" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -15007,7 +15052,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="76" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -15027,7 +15072,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="76" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -15047,7 +15092,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="76" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -15067,7 +15112,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="76" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -15087,7 +15132,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="76" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -15107,7 +15152,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="76" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -15127,7 +15172,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="76" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -15147,7 +15192,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="76" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -15167,7 +15212,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="76" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -15187,7 +15232,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="76" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -15207,7 +15252,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="75.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="76" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
